--- a/data/verification/verification_pending.xlsx
+++ b/data/verification/verification_pending.xlsx
@@ -440,7 +440,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K508"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
@@ -548,10 +548,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Scaffold and substituents preserved (perfect layer)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -589,10 +593,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Scaffold and substituents preserved (perfect layer)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -618,7 +626,6 @@
       <c r="E4" t="n">
         <v>4</v>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>CN108329274.png</t>
@@ -629,7 +636,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -655,7 +661,6 @@
       <c r="E5" t="n">
         <v>31</v>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>CN108341814.png</t>
@@ -666,7 +671,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -704,10 +708,14 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Phthalazinone core and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -745,10 +753,14 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Quinazoline core and substituents preserved in both picks</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -774,7 +786,6 @@
       <c r="E8" t="n">
         <v>46</v>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>CN108467370.png</t>
@@ -782,10 +793,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Quinazoline core and substituents preserved in both picks</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -811,7 +826,6 @@
       <c r="E9" t="n">
         <v>8</v>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>CN109134336.png</t>
@@ -819,10 +833,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -848,7 +866,6 @@
       <c r="E10" t="n">
         <v>27</v>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>CN109134434.png</t>
@@ -856,10 +873,14 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Decoded molecule 1 preserves the fused-ring scaffold shown on the page</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -885,7 +906,6 @@
       <c r="E11" t="n">
         <v>14</v>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>CN109134448.png</t>
@@ -896,7 +916,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -922,7 +941,6 @@
       <c r="E12" t="n">
         <v>25</v>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>CN109678803.png</t>
@@ -930,10 +948,14 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic scaffold and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -974,7 +996,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1015,7 +1036,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1053,10 +1073,14 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Bicyclic heteroaromatic core shared with the page depiction</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1082,7 +1106,6 @@
       <c r="E16" t="n">
         <v>5</v>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>CN109867675.png</t>
@@ -1090,10 +1113,14 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Bicyclic heteroaromatic core shared with the page depiction</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1134,7 +1161,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1160,7 +1186,6 @@
       <c r="E18" t="n">
         <v>15</v>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>CN110028509.png</t>
@@ -1171,7 +1196,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1197,7 +1221,6 @@
       <c r="E19" t="n">
         <v>11</v>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>CN110078724.png</t>
@@ -1205,10 +1228,14 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Succinimide-indole scaffold matches (reconfirmed on full sheet)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1246,10 +1273,14 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Quinazoline-type core preserved in both picks</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1287,10 +1318,14 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Quinazoline-type core preserved in both picks</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1328,10 +1363,14 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1357,7 +1396,6 @@
       <c r="E23" t="n">
         <v>4</v>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>CN110305140.png</t>
@@ -1365,10 +1403,14 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1409,7 +1451,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1450,7 +1491,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1488,10 +1528,14 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic core and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1529,10 +1573,14 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic core and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1573,7 +1621,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1599,7 +1646,6 @@
       <c r="E29" t="n">
         <v>4</v>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>CN111410667.png</t>
@@ -1610,7 +1656,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1648,10 +1693,14 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Same heterocyclic system, ring count and substituent positions</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1689,10 +1738,14 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Same heterocyclic system, ring count and substituent positions</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1718,7 +1771,6 @@
       <c r="E32" t="n">
         <v>30</v>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>CN111518051.png</t>
@@ -1729,7 +1781,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1755,7 +1806,6 @@
       <c r="E33" t="n">
         <v>5</v>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>CN111518082.png</t>
@@ -1763,10 +1813,14 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Fused polycyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1804,10 +1858,14 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic scaffold and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1833,7 +1891,6 @@
       <c r="E35" t="n">
         <v>24</v>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>CN111620878A.png</t>
@@ -1841,10 +1898,14 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic scaffold and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1870,7 +1931,6 @@
       <c r="E36" t="n">
         <v>7</v>
       </c>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>CN111825719.png</t>
@@ -1881,7 +1941,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1922,7 +1981,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1948,7 +2006,6 @@
       <c r="E38" t="n">
         <v>76</v>
       </c>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>CN112174935.png</t>
@@ -1959,7 +2016,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2000,7 +2056,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2026,7 +2081,6 @@
       <c r="E40" t="n">
         <v>95</v>
       </c>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>CN112409334.png</t>
@@ -2037,7 +2091,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2075,10 +2128,14 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2116,10 +2173,14 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2160,7 +2221,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2201,7 +2261,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2227,7 +2286,6 @@
       <c r="E45" t="n">
         <v>6</v>
       </c>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>CN113248448.png</t>
@@ -2235,10 +2293,14 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Heterocyclic core preserved (3:31b)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2264,7 +2326,6 @@
       <c r="E46" t="n">
         <v>9</v>
       </c>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>CN113292510.png</t>
@@ -2272,10 +2333,14 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic core and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2316,7 +2381,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2342,7 +2406,6 @@
       <c r="E48" t="n">
         <v>28</v>
       </c>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>CN113480479.png</t>
@@ -2353,7 +2416,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2379,7 +2441,6 @@
       <c r="E49" t="n">
         <v>12</v>
       </c>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>CN113773275.png</t>
@@ -2387,10 +2448,14 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Fused bicyclic heterocycle and substituent arrangement preserved (ZONK2003-18)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2416,7 +2481,6 @@
       <c r="E50" t="n">
         <v>13</v>
       </c>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>CN113880845.png</t>
@@ -2424,10 +2488,14 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic core and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2468,7 +2536,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2509,7 +2576,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2547,10 +2613,14 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic core and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2588,10 +2658,14 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic core and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2617,7 +2691,6 @@
       <c r="E55" t="n">
         <v>15</v>
       </c>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>CN114716440.png</t>
@@ -2625,10 +2698,14 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic scaffold and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2669,7 +2746,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2710,7 +2786,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2751,7 +2826,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2792,7 +2866,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2833,7 +2906,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2859,7 +2931,6 @@
       <c r="E61" t="n">
         <v>95</v>
       </c>
-      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
           <t>CN115721648.png</t>
@@ -2870,7 +2941,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2911,7 +2981,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2952,7 +3021,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2990,10 +3058,14 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic core and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3019,7 +3091,6 @@
       <c r="E65" t="n">
         <v>7</v>
       </c>
-      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>CN115872947.png</t>
@@ -3027,10 +3098,14 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic core and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3068,10 +3143,14 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Bicyclic heteroaromatic core preserved</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3109,10 +3188,14 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Bicyclic heteroaromatic core preserved</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3138,7 +3221,6 @@
       <c r="E68" t="n">
         <v>9</v>
       </c>
-      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
           <t>CN115974872.png</t>
@@ -3146,10 +3228,14 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Heterocyclic scaffold and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3175,7 +3261,6 @@
       <c r="E69" t="n">
         <v>4</v>
       </c>
-      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
           <t>CN116283658.png</t>
@@ -3183,10 +3268,14 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic core and substituent pattern preserved (YB-6)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3224,10 +3313,14 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3265,10 +3358,14 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3306,10 +3403,14 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Fused bicyclic system and key heteroatoms preserved</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3347,10 +3448,14 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Fused bicyclic system and key heteroatoms preserved</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3391,7 +3496,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3417,7 +3521,6 @@
       <c r="E75" t="n">
         <v>33</v>
       </c>
-      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
           <t>CN117917402.png</t>
@@ -3428,7 +3531,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3454,7 +3556,6 @@
       <c r="E76" t="n">
         <v>71</v>
       </c>
-      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
           <t>CN118459466.png</t>
@@ -3465,7 +3566,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3503,10 +3603,14 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3532,7 +3636,6 @@
       <c r="E78" t="n">
         <v>34</v>
       </c>
-      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
           <t>CN118496213.png</t>
@@ -3540,10 +3643,14 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3581,10 +3688,14 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic core and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3622,10 +3733,14 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic core and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3663,10 +3778,14 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3704,10 +3823,14 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3748,7 +3871,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3774,7 +3896,6 @@
       <c r="E84" t="n">
         <v>2</v>
       </c>
-      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
           <t>CN119039190.png</t>
@@ -3785,7 +3906,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3823,10 +3943,14 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Fused-ring core topology preserved (reconfirmed on full sheet)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3852,7 +3976,6 @@
       <c r="E86" t="n">
         <v>19</v>
       </c>
-      <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
           <t>CN119161363.png</t>
@@ -3860,10 +3983,14 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Fused-ring core topology preserved (reconfirmed on full sheet)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3901,10 +4028,14 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3930,7 +4061,6 @@
       <c r="E88" t="n">
         <v>69</v>
       </c>
-      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
           <t>CN119591581.png</t>
@@ -3938,10 +4068,14 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3982,7 +4116,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4008,7 +4141,6 @@
       <c r="E90" t="n">
         <v>13</v>
       </c>
-      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
           <t>EP3553052.png</t>
@@ -4019,7 +4151,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4060,7 +4191,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4086,7 +4216,6 @@
       <c r="E92" t="n">
         <v>30</v>
       </c>
-      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
           <t>US11319319.png</t>
@@ -4097,7 +4226,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4135,10 +4263,14 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic scaffold and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4164,7 +4296,6 @@
       <c r="E94" t="n">
         <v>34</v>
       </c>
-      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
           <t>US2011217300.png</t>
@@ -4172,10 +4303,14 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic scaffold and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4213,10 +4348,14 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4242,7 +4381,6 @@
       <c r="E96" t="n">
         <v>32</v>
       </c>
-      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
           <t>US2012302631.png</t>
@@ -4250,10 +4388,14 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4279,7 +4421,6 @@
       <c r="E97" t="n">
         <v>43</v>
       </c>
-      <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
           <t>US2016362390.png</t>
@@ -4287,10 +4428,14 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4316,7 +4461,6 @@
       <c r="E98" t="n">
         <v>2</v>
       </c>
-      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
           <t>US2019062302.png</t>
@@ -4324,10 +4468,14 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>N-heterocyclic scaffold and ring count preserved</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4368,7 +4516,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4394,7 +4541,6 @@
       <c r="E100" t="n">
         <v>22</v>
       </c>
-      <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
           <t>US2019119275.png</t>
@@ -4405,7 +4551,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4446,7 +4591,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4487,7 +4631,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4528,7 +4671,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4554,7 +4696,6 @@
       <c r="E104" t="n">
         <v>136</v>
       </c>
-      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
           <t>US2020317691.png</t>
@@ -4565,7 +4706,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4603,10 +4743,14 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>uncertain (visual)</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Pick 1 spirocyclic core matches; pick 2 similar-but-incomplete (benzene ring appears missing) — flagged for human judgment</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4644,10 +4788,14 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>uncertain (visual)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Pick 1 spirocyclic core matches; pick 2 similar-but-incomplete (benzene ring appears missing) — flagged for human judgment</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4688,7 +4836,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4729,7 +4876,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4767,10 +4913,14 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Fused bicyclic heterocyclic core and substituent pattern preserved</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4796,7 +4946,6 @@
       <c r="E110" t="n">
         <v>26</v>
       </c>
-      <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
           <t>US2021340143.png</t>
@@ -4804,10 +4953,14 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Fused bicyclic heterocyclic core and substituent pattern preserved</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4848,7 +5001,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4889,7 +5041,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4927,10 +5078,14 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4956,7 +5111,6 @@
       <c r="E114" t="n">
         <v>49</v>
       </c>
-      <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
           <t>US2022339129.png</t>
@@ -4964,10 +5118,14 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5008,7 +5166,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5034,7 +5191,6 @@
       <c r="E116" t="n">
         <v>32</v>
       </c>
-      <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
           <t>US2022340567.png</t>
@@ -5045,7 +5201,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5086,7 +5241,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5127,7 +5281,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5168,7 +5321,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5194,7 +5346,6 @@
       <c r="E120" t="n">
         <v>31</v>
       </c>
-      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
           <t>US2023159526.png</t>
@@ -5205,7 +5356,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5246,7 +5396,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5272,7 +5421,6 @@
       <c r="E122" t="n">
         <v>60</v>
       </c>
-      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
           <t>US2023331693.png</t>
@@ -5283,7 +5431,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5324,7 +5471,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5350,7 +5496,6 @@
       <c r="E124" t="n">
         <v>31</v>
       </c>
-      <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
           <t>US2024158396.png</t>
@@ -5361,7 +5506,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5387,7 +5531,6 @@
       <c r="E125" t="n">
         <v>36</v>
       </c>
-      <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
           <t>US2024174668.png</t>
@@ -5398,7 +5541,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5436,10 +5578,14 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Fused bicyclic heterocyclic core shared with the page</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5477,10 +5623,14 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Fused bicyclic heterocyclic core shared with the page</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5521,7 +5671,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5547,7 +5696,6 @@
       <c r="E129" t="n">
         <v>32</v>
       </c>
-      <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
           <t>US2024360128.png</t>
@@ -5558,7 +5706,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5599,7 +5746,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5625,7 +5771,6 @@
       <c r="E131" t="n">
         <v>60</v>
       </c>
-      <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
           <t>US2025084056.png</t>
@@ -5636,7 +5781,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5677,7 +5821,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5703,7 +5846,6 @@
       <c r="E133" t="n">
         <v>61</v>
       </c>
-      <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
           <t>US2025092012.png</t>
@@ -5714,7 +5856,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5752,10 +5893,14 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5781,7 +5926,6 @@
       <c r="E135" t="n">
         <v>24</v>
       </c>
-      <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
           <t>US8349899.png</t>
@@ -5789,10 +5933,14 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5830,10 +5978,14 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Same pyrazolo-fused ring system as depicted</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5859,7 +6011,6 @@
       <c r="E137" t="n">
         <v>23</v>
       </c>
-      <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
           <t>US8765817.png</t>
@@ -5867,10 +6018,14 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Same pyrazolo-fused ring system as depicted</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5911,7 +6066,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5952,7 +6106,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5993,7 +6146,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6034,7 +6186,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6075,7 +6226,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6116,7 +6266,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6157,7 +6306,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6198,7 +6346,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6236,10 +6383,14 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Fused polycyclic scaffold preserved</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6277,10 +6428,14 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Fused polycyclic scaffold preserved</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6321,7 +6476,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6347,7 +6501,6 @@
       <c r="E149" t="n">
         <v>70</v>
       </c>
-      <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
         <is>
           <t>WO2006074293.png</t>
@@ -6358,7 +6511,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6399,7 +6551,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6440,7 +6591,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6481,7 +6631,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6522,7 +6671,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6560,10 +6708,14 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Bicyclic heteroaromatic core and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6589,7 +6741,6 @@
       <c r="E155" t="n">
         <v>185</v>
       </c>
-      <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr">
         <is>
           <t>WO2007096393.png</t>
@@ -6597,10 +6748,14 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Bicyclic heteroaromatic core and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6626,7 +6781,6 @@
       <c r="E156" t="n">
         <v>105</v>
       </c>
-      <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr">
         <is>
           <t>WO2007096395.png</t>
@@ -6634,10 +6788,14 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Fused bicyclic parent core preserved</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6675,10 +6833,14 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6716,10 +6878,14 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6760,7 +6926,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6801,7 +6966,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6839,10 +7003,14 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Fused tricyclic scaffold preserved</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6880,10 +7048,14 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Fused tricyclic scaffold preserved</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6924,7 +7096,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6950,7 +7121,6 @@
       <c r="E164" t="n">
         <v>70</v>
       </c>
-      <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr">
         <is>
           <t>WO2009053373.png</t>
@@ -6961,7 +7131,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6999,10 +7168,14 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -7028,7 +7201,6 @@
       <c r="E166" t="n">
         <v>150</v>
       </c>
-      <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr">
         <is>
           <t>WO2009097287.png</t>
@@ -7036,10 +7208,14 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -7077,10 +7253,14 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Fused heterobicyclic core and substituent layout preserved</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -7106,7 +7286,6 @@
       <c r="E168" t="n">
         <v>18</v>
       </c>
-      <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr">
         <is>
           <t>WO2009111354.png</t>
@@ -7114,10 +7293,14 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Fused heterobicyclic core and substituent layout preserved</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7158,7 +7341,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -7184,7 +7366,6 @@
       <c r="E170" t="n">
         <v>53</v>
       </c>
-      <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr">
         <is>
           <t>WO2009118382.png</t>
@@ -7195,7 +7376,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -7236,7 +7416,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -7277,7 +7456,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -7318,7 +7496,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -7359,7 +7536,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -7400,7 +7576,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -7441,7 +7616,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -7482,7 +7656,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -7523,7 +7696,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -7549,7 +7721,6 @@
       <c r="E179" t="n">
         <v>43</v>
       </c>
-      <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr">
         <is>
           <t>WO2011084439.png</t>
@@ -7557,10 +7728,14 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -7601,7 +7776,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -7642,7 +7816,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -7683,7 +7856,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -7709,7 +7881,6 @@
       <c r="E183" t="n">
         <v>66</v>
       </c>
-      <c r="F183" t="inlineStr"/>
       <c r="G183" t="inlineStr">
         <is>
           <t>WO2011128381.png</t>
@@ -7720,7 +7891,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -7758,10 +7928,14 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Fused ring system preserved</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -7799,10 +7973,14 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Fused ring system preserved</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -7843,7 +8021,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -7869,7 +8046,6 @@
       <c r="E187" t="n">
         <v>88</v>
       </c>
-      <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr">
         <is>
           <t>WO2012035171.png</t>
@@ -7880,7 +8056,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -7921,7 +8096,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -7962,7 +8136,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -8003,7 +8176,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -8044,7 +8216,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -8085,7 +8256,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -8126,7 +8296,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -8167,7 +8336,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -8208,7 +8376,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -8249,7 +8416,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -8290,7 +8456,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -8328,10 +8493,14 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Fused polycyclic system and heteroatoms preserved</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -8369,10 +8538,14 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Fused polycyclic system and heteroatoms preserved</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -8413,7 +8586,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -8439,7 +8611,6 @@
       <c r="E201" t="n">
         <v>62</v>
       </c>
-      <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr">
         <is>
           <t>WO2015049325.png</t>
@@ -8450,7 +8621,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -8491,7 +8661,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -8532,7 +8701,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -8558,7 +8726,6 @@
       <c r="E204" t="n">
         <v>44</v>
       </c>
-      <c r="F204" t="inlineStr"/>
       <c r="G204" t="inlineStr">
         <is>
           <t>WO2016009076.png</t>
@@ -8569,7 +8736,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -8595,7 +8761,6 @@
       <c r="E205" t="n">
         <v>99</v>
       </c>
-      <c r="F205" t="inlineStr"/>
       <c r="G205" t="inlineStr">
         <is>
           <t>WO2016026549.png</t>
@@ -8606,7 +8771,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -8647,7 +8811,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -8673,7 +8836,6 @@
       <c r="E207" t="n">
         <v>120</v>
       </c>
-      <c r="F207" t="inlineStr"/>
       <c r="G207" t="inlineStr">
         <is>
           <t>WO2016041618.png</t>
@@ -8684,7 +8846,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -8722,10 +8883,14 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic scaffold and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -8763,10 +8928,14 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic scaffold and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -8792,7 +8961,6 @@
       <c r="E210" t="n">
         <v>183</v>
       </c>
-      <c r="F210" t="inlineStr"/>
       <c r="G210" t="inlineStr">
         <is>
           <t>WO2016144825.png</t>
@@ -8800,10 +8968,14 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I210" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Heterocyclic core and substituent pattern preserved</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -8841,10 +9013,14 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -8870,7 +9046,6 @@
       <c r="E212" t="n">
         <v>118</v>
       </c>
-      <c r="F212" t="inlineStr"/>
       <c r="G212" t="inlineStr">
         <is>
           <t>WO2016144826.png</t>
@@ -8878,10 +9053,14 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -8907,7 +9086,6 @@
       <c r="E213" t="n">
         <v>173</v>
       </c>
-      <c r="F213" t="inlineStr"/>
       <c r="G213" t="inlineStr">
         <is>
           <t>WO2016145045.png</t>
@@ -8915,10 +9093,14 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Heterocyclic core and key substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -8959,7 +9141,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -9000,7 +9181,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -9041,7 +9221,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -9067,7 +9246,6 @@
       <c r="E217" t="n">
         <v>207</v>
       </c>
-      <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr">
         <is>
           <t>WO2016180537.png</t>
@@ -9078,7 +9256,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -9119,7 +9296,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -9145,7 +9321,6 @@
       <c r="E219" t="n">
         <v>52</v>
       </c>
-      <c r="F219" t="inlineStr"/>
       <c r="G219" t="inlineStr">
         <is>
           <t>WO2017042100.png</t>
@@ -9156,7 +9331,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -9197,7 +9371,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -9238,7 +9411,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -9279,7 +9451,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -9320,7 +9491,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -9358,10 +9528,14 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I224" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -9387,7 +9561,6 @@
       <c r="E225" t="n">
         <v>19</v>
       </c>
-      <c r="F225" t="inlineStr"/>
       <c r="G225" t="inlineStr">
         <is>
           <t>WO2018077227.png</t>
@@ -9395,10 +9568,14 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -9424,7 +9601,6 @@
       <c r="E226" t="n">
         <v>27</v>
       </c>
-      <c r="F226" t="inlineStr"/>
       <c r="G226" t="inlineStr">
         <is>
           <t>WO2018077246.png</t>
@@ -9432,10 +9608,14 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I226" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic core and substituent layout preserved</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -9476,7 +9656,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -9517,7 +9696,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -9558,7 +9736,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -9599,7 +9776,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -9640,7 +9816,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -9681,7 +9856,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -9722,7 +9896,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -9763,7 +9936,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -9804,7 +9976,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -9830,7 +10001,6 @@
       <c r="E236" t="n">
         <v>82</v>
       </c>
-      <c r="F236" t="inlineStr"/>
       <c r="G236" t="inlineStr">
         <is>
           <t>WO2018081091.png</t>
@@ -9841,7 +10011,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -9879,10 +10048,14 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -9920,10 +10093,14 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I238" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -9961,10 +10138,14 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I239" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -9990,7 +10171,6 @@
       <c r="E240" t="n">
         <v>83</v>
       </c>
-      <c r="F240" t="inlineStr"/>
       <c r="G240" t="inlineStr">
         <is>
           <t>WO2018087126.png</t>
@@ -9998,10 +10178,14 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I240" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -10042,7 +10226,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -10068,7 +10251,6 @@
       <c r="E242" t="n">
         <v>95</v>
       </c>
-      <c r="F242" t="inlineStr"/>
       <c r="G242" t="inlineStr">
         <is>
           <t>WO2018100070.png</t>
@@ -10079,7 +10261,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -10120,7 +10301,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -10146,7 +10326,6 @@
       <c r="E244" t="n">
         <v>95</v>
       </c>
-      <c r="F244" t="inlineStr"/>
       <c r="G244" t="inlineStr">
         <is>
           <t>WO2018107060.png</t>
@@ -10157,7 +10336,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -10198,7 +10376,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -10239,7 +10416,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -10280,7 +10456,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -10306,7 +10481,6 @@
       <c r="E248" t="n">
         <v>89</v>
       </c>
-      <c r="F248" t="inlineStr"/>
       <c r="G248" t="inlineStr">
         <is>
           <t>WO2018122212.png</t>
@@ -10317,7 +10491,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -10343,7 +10516,6 @@
       <c r="E249" t="n">
         <v>19</v>
       </c>
-      <c r="F249" t="inlineStr"/>
       <c r="G249" t="inlineStr">
         <is>
           <t>WO2018134213.png</t>
@@ -10354,7 +10526,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -10395,7 +10566,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -10421,7 +10591,6 @@
       <c r="E251" t="n">
         <v>171</v>
       </c>
-      <c r="F251" t="inlineStr"/>
       <c r="G251" t="inlineStr">
         <is>
           <t>WO2018136264.png</t>
@@ -10432,7 +10601,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -10473,7 +10641,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -10499,7 +10666,6 @@
       <c r="E253" t="n">
         <v>234</v>
       </c>
-      <c r="F253" t="inlineStr"/>
       <c r="G253" t="inlineStr">
         <is>
           <t>WO2018136265.png</t>
@@ -10510,7 +10676,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -10548,10 +10713,14 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I254" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Heterocyclic scaffold and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -10589,10 +10758,14 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I255" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Heterocyclic scaffold and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -10633,7 +10806,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -10659,7 +10831,6 @@
       <c r="E257" t="n">
         <v>70</v>
       </c>
-      <c r="F257" t="inlineStr"/>
       <c r="G257" t="inlineStr">
         <is>
           <t>WO2018154088.png</t>
@@ -10670,7 +10841,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -10708,10 +10878,14 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I258" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic scaffold and substituents preserved (range-ID patent)</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -10737,7 +10911,6 @@
       <c r="E259" t="n">
         <v>81</v>
       </c>
-      <c r="F259" t="inlineStr"/>
       <c r="G259" t="inlineStr">
         <is>
           <t>WO2018165395.png</t>
@@ -10745,10 +10918,14 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I259" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic scaffold and substituents preserved (range-ID patent)</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -10786,10 +10963,14 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I260" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic core and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -10827,10 +11008,14 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I261" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic core and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -10856,7 +11041,6 @@
       <c r="E262" t="n">
         <v>53</v>
       </c>
-      <c r="F262" t="inlineStr"/>
       <c r="G262" t="inlineStr">
         <is>
           <t>WO2018167147.png</t>
@@ -10867,7 +11051,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -10905,10 +11088,14 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I263" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>Heterocyclic scaffold and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -10934,7 +11121,6 @@
       <c r="E264" t="n">
         <v>117</v>
       </c>
-      <c r="F264" t="inlineStr"/>
       <c r="G264" t="inlineStr">
         <is>
           <t>WO2018172984.png</t>
@@ -10942,10 +11128,14 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I264" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>Heterocyclic scaffold and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -10971,7 +11161,6 @@
       <c r="E265" t="n">
         <v>29</v>
       </c>
-      <c r="F265" t="inlineStr"/>
       <c r="G265" t="inlineStr">
         <is>
           <t>WO2018206739.png</t>
@@ -10982,7 +11171,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -11020,10 +11208,14 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I266" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>Heterocyclic core and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -11049,7 +11241,6 @@
       <c r="E267" t="n">
         <v>110</v>
       </c>
-      <c r="F267" t="inlineStr"/>
       <c r="G267" t="inlineStr">
         <is>
           <t>WO2018213632.png</t>
@@ -11057,10 +11248,14 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I267" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>Heterocyclic core and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -11101,7 +11296,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -11127,7 +11321,6 @@
       <c r="E269" t="n">
         <v>177</v>
       </c>
-      <c r="F269" t="inlineStr"/>
       <c r="G269" t="inlineStr">
         <is>
           <t>WO2018215668.png</t>
@@ -11138,7 +11331,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -11179,7 +11371,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -11220,7 +11411,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -11261,7 +11451,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -11287,7 +11476,6 @@
       <c r="E273" t="n">
         <v>162</v>
       </c>
-      <c r="F273" t="inlineStr"/>
       <c r="G273" t="inlineStr">
         <is>
           <t>WO2019012063.png</t>
@@ -11298,7 +11486,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -11336,10 +11523,14 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I274" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -11365,7 +11556,6 @@
       <c r="E275" t="n">
         <v>102</v>
       </c>
-      <c r="F275" t="inlineStr"/>
       <c r="G275" t="inlineStr">
         <is>
           <t>WO2019027960.png</t>
@@ -11373,10 +11563,14 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I275" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -11414,10 +11608,14 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I276" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -11455,10 +11653,14 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I277" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -11484,7 +11686,6 @@
       <c r="E278" t="n">
         <v>49</v>
       </c>
-      <c r="F278" t="inlineStr"/>
       <c r="G278" t="inlineStr">
         <is>
           <t>WO2019067843.png</t>
@@ -11492,10 +11693,14 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I278" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -11536,7 +11741,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -11577,7 +11781,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -11618,7 +11821,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -11644,7 +11846,6 @@
       <c r="E282" t="n">
         <v>167</v>
       </c>
-      <c r="F282" t="inlineStr"/>
       <c r="G282" t="inlineStr">
         <is>
           <t>WO2019075265.png</t>
@@ -11655,7 +11856,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -11693,10 +11893,14 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I283" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic core and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -11722,7 +11926,6 @@
       <c r="E284" t="n">
         <v>97</v>
       </c>
-      <c r="F284" t="inlineStr"/>
       <c r="G284" t="inlineStr">
         <is>
           <t>WO2019090198.png</t>
@@ -11730,10 +11933,14 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I284" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic core and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -11774,7 +11981,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -11800,7 +12006,6 @@
       <c r="E286" t="n">
         <v>119</v>
       </c>
-      <c r="F286" t="inlineStr"/>
       <c r="G286" t="inlineStr">
         <is>
           <t>WO2019118909.png</t>
@@ -11811,7 +12016,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -11852,7 +12056,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -11893,7 +12096,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -11934,7 +12136,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -11960,7 +12161,6 @@
       <c r="E290" t="n">
         <v>113</v>
       </c>
-      <c r="F290" t="inlineStr"/>
       <c r="G290" t="inlineStr">
         <is>
           <t>WO2019158019.png</t>
@@ -11971,7 +12171,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -12009,10 +12208,14 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I291" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -12050,10 +12253,14 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I292" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -12094,7 +12301,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -12120,7 +12326,6 @@
       <c r="E294" t="n">
         <v>155</v>
       </c>
-      <c r="F294" t="inlineStr"/>
       <c r="G294" t="inlineStr">
         <is>
           <t>WO2019183364.png</t>
@@ -12131,7 +12336,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -12169,10 +12373,14 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I295" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>Heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -12198,7 +12406,6 @@
       <c r="E296" t="n">
         <v>334</v>
       </c>
-      <c r="F296" t="inlineStr"/>
       <c r="G296" t="inlineStr">
         <is>
           <t>WO2019183367.png</t>
@@ -12206,10 +12413,14 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I296" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>Heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -12235,7 +12446,6 @@
       <c r="E297" t="n">
         <v>119</v>
       </c>
-      <c r="F297" t="inlineStr"/>
       <c r="G297" t="inlineStr">
         <is>
           <t>WO2019191227.png</t>
@@ -12243,10 +12453,14 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I297" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic core and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -12284,10 +12498,14 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I298" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>Heterocyclic scaffold and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -12325,10 +12543,14 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I299" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>Heterocyclic scaffold and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -12369,7 +12591,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -12395,7 +12616,6 @@
       <c r="E301" t="n">
         <v>296</v>
       </c>
-      <c r="F301" t="inlineStr"/>
       <c r="G301" t="inlineStr">
         <is>
           <t>WO2019200120.png</t>
@@ -12406,7 +12626,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -12447,7 +12666,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -12473,7 +12691,6 @@
       <c r="E303" t="n">
         <v>52</v>
       </c>
-      <c r="F303" t="inlineStr"/>
       <c r="G303" t="inlineStr">
         <is>
           <t>WO2019204537.png</t>
@@ -12484,7 +12701,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -12510,7 +12726,6 @@
       <c r="E304" t="n">
         <v>168</v>
       </c>
-      <c r="F304" t="inlineStr"/>
       <c r="G304" t="inlineStr">
         <is>
           <t>WO2019206049.png</t>
@@ -12518,10 +12733,14 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I304" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -12559,10 +12778,14 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I305" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -12600,10 +12823,14 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I306" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -12644,7 +12871,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -12685,7 +12911,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -12726,7 +12951,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -12752,7 +12976,6 @@
       <c r="E310" t="n">
         <v>238</v>
       </c>
-      <c r="F310" t="inlineStr"/>
       <c r="G310" t="inlineStr">
         <is>
           <t>WO2019238067.png</t>
@@ -12763,7 +12986,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -12804,7 +13026,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -12830,7 +13051,6 @@
       <c r="E312" t="n">
         <v>113</v>
       </c>
-      <c r="F312" t="inlineStr"/>
       <c r="G312" t="inlineStr">
         <is>
           <t>WO2019238929.png</t>
@@ -12841,7 +13061,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -12882,7 +13101,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -12908,7 +13126,6 @@
       <c r="E314" t="n">
         <v>113</v>
       </c>
-      <c r="F314" t="inlineStr"/>
       <c r="G314" t="inlineStr">
         <is>
           <t>WO2019243822.png</t>
@@ -12919,7 +13136,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -12957,10 +13173,14 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I315" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic core and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -12998,10 +13218,14 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I316" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic core and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -13042,7 +13266,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -13068,7 +13291,6 @@
       <c r="E318" t="n">
         <v>25</v>
       </c>
-      <c r="F318" t="inlineStr"/>
       <c r="G318" t="inlineStr">
         <is>
           <t>WO2020001420.png</t>
@@ -13079,7 +13301,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -13117,10 +13338,14 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I319" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic scaffold and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -13158,10 +13383,14 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I320" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic scaffold and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -13202,7 +13431,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -13243,7 +13471,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -13281,10 +13508,14 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I323" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>Heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -13310,7 +13541,6 @@
       <c r="E324" t="n">
         <v>166</v>
       </c>
-      <c r="F324" t="inlineStr"/>
       <c r="G324" t="inlineStr">
         <is>
           <t>WO2020080979.png</t>
@@ -13318,10 +13548,14 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I324" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>Heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -13359,10 +13593,14 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I325" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -13400,10 +13638,14 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I326" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -13444,7 +13686,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -13485,7 +13726,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -13526,7 +13766,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -13567,7 +13806,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -13605,10 +13843,14 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I331" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -13634,7 +13876,6 @@
       <c r="E332" t="n">
         <v>93</v>
       </c>
-      <c r="F332" t="inlineStr"/>
       <c r="G332" t="inlineStr">
         <is>
           <t>WO2020120257.png</t>
@@ -13642,10 +13883,14 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I332" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -13686,7 +13931,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -13712,7 +13956,6 @@
       <c r="E334" t="n">
         <v>174</v>
       </c>
-      <c r="F334" t="inlineStr"/>
       <c r="G334" t="inlineStr">
         <is>
           <t>WO2020141470.png</t>
@@ -13723,7 +13966,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -13764,7 +14006,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -13790,7 +14031,6 @@
       <c r="E336" t="n">
         <v>11</v>
       </c>
-      <c r="F336" t="inlineStr"/>
       <c r="G336" t="inlineStr">
         <is>
           <t>WO2020188467.png</t>
@@ -13801,7 +14041,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -13842,7 +14081,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -13868,7 +14106,6 @@
       <c r="E338" t="n">
         <v>130</v>
       </c>
-      <c r="F338" t="inlineStr"/>
       <c r="G338" t="inlineStr">
         <is>
           <t>WO2020193511.png</t>
@@ -13879,7 +14116,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -13920,7 +14156,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -13946,7 +14181,6 @@
       <c r="E340" t="n">
         <v>94</v>
       </c>
-      <c r="F340" t="inlineStr"/>
       <c r="G340" t="inlineStr">
         <is>
           <t>WO2020193512.png</t>
@@ -13957,7 +14191,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -13983,7 +14216,6 @@
       <c r="E341" t="n">
         <v>177</v>
       </c>
-      <c r="F341" t="inlineStr"/>
       <c r="G341" t="inlineStr">
         <is>
           <t>WO2020200291.png</t>
@@ -13994,7 +14226,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -14032,10 +14263,14 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I342" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>Heterocyclic core and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -14073,10 +14308,14 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I343" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>Heterocyclic core and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -14117,7 +14356,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -14158,7 +14396,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -14199,7 +14436,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -14225,7 +14461,6 @@
       <c r="E347" t="n">
         <v>186</v>
       </c>
-      <c r="F347" t="inlineStr"/>
       <c r="G347" t="inlineStr">
         <is>
           <t>WO2020237025.png</t>
@@ -14236,7 +14471,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -14277,7 +14511,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -14303,7 +14536,6 @@
       <c r="E349" t="n">
         <v>59</v>
       </c>
-      <c r="F349" t="inlineStr"/>
       <c r="G349" t="inlineStr">
         <is>
           <t>WO2020247418.png</t>
@@ -14314,7 +14546,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -14352,10 +14583,14 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I350" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -14393,10 +14628,14 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I351" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -14434,10 +14673,14 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I352" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -14475,10 +14718,14 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I353" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -14516,10 +14763,14 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I354" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -14545,7 +14796,6 @@
       <c r="E355" t="n">
         <v>30</v>
       </c>
-      <c r="F355" t="inlineStr"/>
       <c r="G355" t="inlineStr">
         <is>
           <t>WO2020254565.png</t>
@@ -14553,10 +14803,14 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I355" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -14594,10 +14848,14 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I356" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -14635,10 +14893,14 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I357" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -14664,7 +14926,6 @@
       <c r="E358" t="n">
         <v>113</v>
       </c>
-      <c r="F358" t="inlineStr"/>
       <c r="G358" t="inlineStr">
         <is>
           <t>WO2020254572.png</t>
@@ -14675,7 +14936,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -14716,7 +14976,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -14742,7 +15001,6 @@
       <c r="E360" t="n">
         <v>85</v>
       </c>
-      <c r="F360" t="inlineStr"/>
       <c r="G360" t="inlineStr">
         <is>
           <t>WO2020254697.png</t>
@@ -14753,7 +15011,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -14779,7 +15036,6 @@
       <c r="E361" t="n">
         <v>8</v>
       </c>
-      <c r="F361" t="inlineStr"/>
       <c r="G361" t="inlineStr">
         <is>
           <t>WO2021000912.png</t>
@@ -14790,7 +15046,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -14816,7 +15071,6 @@
       <c r="E362" t="n">
         <v>60</v>
       </c>
-      <c r="F362" t="inlineStr"/>
       <c r="G362" t="inlineStr">
         <is>
           <t>WO2021000925.png</t>
@@ -14827,7 +15081,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -14868,7 +15121,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -14894,7 +15146,6 @@
       <c r="E364" t="n">
         <v>33</v>
       </c>
-      <c r="F364" t="inlineStr"/>
       <c r="G364" t="inlineStr">
         <is>
           <t>WO2021004535.png</t>
@@ -14905,7 +15156,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -14943,10 +15193,14 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I365" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>Heterocyclic scaffold and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -14972,7 +15226,6 @@
       <c r="E366" t="n">
         <v>56</v>
       </c>
-      <c r="F366" t="inlineStr"/>
       <c r="G366" t="inlineStr">
         <is>
           <t>WO2021013083.png</t>
@@ -14980,10 +15233,14 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I366" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>Heterocyclic scaffold and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -15021,10 +15278,14 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I367" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>Compound 4 correspondence reconfirmed on full sheet</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -15062,10 +15323,14 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I368" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>Compound 4 correspondence reconfirmed on full sheet</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -15106,7 +15371,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -15132,7 +15396,6 @@
       <c r="E370" t="n">
         <v>138</v>
       </c>
-      <c r="F370" t="inlineStr"/>
       <c r="G370" t="inlineStr">
         <is>
           <t>WO2021046515.png</t>
@@ -15143,7 +15406,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -15181,10 +15443,14 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I371" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic core and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -15210,7 +15476,6 @@
       <c r="E372" t="n">
         <v>135</v>
       </c>
-      <c r="F372" t="inlineStr"/>
       <c r="G372" t="inlineStr">
         <is>
           <t>WO2021062199.png</t>
@@ -15218,10 +15483,14 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I372" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic core and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -15262,7 +15531,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -15288,7 +15556,6 @@
       <c r="E374" t="n">
         <v>84</v>
       </c>
-      <c r="F374" t="inlineStr"/>
       <c r="G374" t="inlineStr">
         <is>
           <t>WO2021084498.png</t>
@@ -15299,7 +15566,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -15340,7 +15606,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -15381,7 +15646,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -15419,10 +15683,14 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I377" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -15460,10 +15728,14 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I378" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -15504,7 +15776,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -15545,7 +15816,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -15571,7 +15841,6 @@
       <c r="E381" t="n">
         <v>29</v>
       </c>
-      <c r="F381" t="inlineStr"/>
       <c r="G381" t="inlineStr">
         <is>
           <t>WO2021108581.png</t>
@@ -15582,7 +15851,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -15608,7 +15876,6 @@
       <c r="E382" t="n">
         <v>65</v>
       </c>
-      <c r="F382" t="inlineStr"/>
       <c r="G382" t="inlineStr">
         <is>
           <t>WO2021113436.png</t>
@@ -15616,10 +15883,14 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I382" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>Heterocyclic scaffold and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -15657,10 +15928,14 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I383" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -15686,7 +15961,6 @@
       <c r="E384" t="n">
         <v>103</v>
       </c>
-      <c r="F384" t="inlineStr"/>
       <c r="G384" t="inlineStr">
         <is>
           <t>WO2021133831.png</t>
@@ -15694,10 +15968,14 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I384" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -15735,10 +16013,14 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I385" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -15776,10 +16058,14 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I386" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -15820,7 +16106,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -15861,7 +16146,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -15902,7 +16186,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -15928,7 +16211,6 @@
       <c r="E390" t="n">
         <v>99</v>
       </c>
-      <c r="F390" t="inlineStr"/>
       <c r="G390" t="inlineStr">
         <is>
           <t>WO2021142203.png</t>
@@ -15939,7 +16221,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -15980,7 +16261,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -16021,7 +16301,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -16059,10 +16338,14 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I393" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -16100,10 +16383,14 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I394" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -16141,10 +16428,14 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I395" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>Fused-ring core and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -16182,10 +16473,14 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I396" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>Fused-ring core and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -16226,7 +16521,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -16267,7 +16561,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -16308,7 +16601,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -16334,7 +16626,6 @@
       <c r="E400" t="n">
         <v>198</v>
       </c>
-      <c r="F400" t="inlineStr"/>
       <c r="G400" t="inlineStr">
         <is>
           <t>WO2021226629.png</t>
@@ -16345,7 +16636,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -16386,7 +16676,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -16412,7 +16701,6 @@
       <c r="E402" t="n">
         <v>45</v>
       </c>
-      <c r="F402" t="inlineStr"/>
       <c r="G402" t="inlineStr">
         <is>
           <t>WO2021228173.png</t>
@@ -16423,7 +16711,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -16461,10 +16748,14 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I403" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic core and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -16502,10 +16793,14 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I404" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic core and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -16546,7 +16841,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -16587,7 +16881,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -16625,10 +16918,14 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I407" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>Fused tricyclic parent core and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -16666,10 +16963,14 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I408" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>Fused tricyclic parent core and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -16710,7 +17011,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -16736,7 +17036,6 @@
       <c r="E410" t="n">
         <v>215</v>
       </c>
-      <c r="F410" t="inlineStr"/>
       <c r="G410" t="inlineStr">
         <is>
           <t>WO2021245070.png</t>
@@ -16747,7 +17046,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -16788,7 +17086,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -16814,7 +17111,6 @@
       <c r="E412" t="n">
         <v>58</v>
       </c>
-      <c r="F412" t="inlineStr"/>
       <c r="G412" t="inlineStr">
         <is>
           <t>WO2021249463.png</t>
@@ -16825,7 +17121,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -16863,10 +17158,14 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I413" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>Heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -16892,7 +17191,6 @@
       <c r="E414" t="n">
         <v>101</v>
       </c>
-      <c r="F414" t="inlineStr"/>
       <c r="G414" t="inlineStr">
         <is>
           <t>WO2021252307.png</t>
@@ -16900,10 +17198,14 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I414" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>Heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -16944,7 +17246,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -16970,7 +17271,6 @@
       <c r="E416" t="n">
         <v>123</v>
       </c>
-      <c r="F416" t="inlineStr"/>
       <c r="G416" t="inlineStr">
         <is>
           <t>WO2021255279.png</t>
@@ -16981,7 +17281,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -17019,10 +17318,14 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I417" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -17060,10 +17363,14 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I418" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -17104,7 +17411,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -17130,7 +17436,6 @@
       <c r="E420" t="n">
         <v>138</v>
       </c>
-      <c r="F420" t="inlineStr"/>
       <c r="G420" t="inlineStr">
         <is>
           <t>WO2022029573.png</t>
@@ -17141,7 +17446,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -17167,7 +17471,6 @@
       <c r="E421" t="n">
         <v>37</v>
       </c>
-      <c r="F421" t="inlineStr"/>
       <c r="G421" t="inlineStr">
         <is>
           <t>WO2022036204.png</t>
@@ -17178,7 +17481,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -17216,10 +17518,14 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I422" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -17257,10 +17563,14 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I423" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -17286,7 +17596,6 @@
       <c r="E424" t="n">
         <v>16</v>
       </c>
-      <c r="F424" t="inlineStr"/>
       <c r="G424" t="inlineStr">
         <is>
           <t>WO2022179524.png</t>
@@ -17294,10 +17603,14 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I424" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -17338,7 +17651,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -17364,7 +17676,6 @@
       <c r="E426" t="n">
         <v>121</v>
       </c>
-      <c r="F426" t="inlineStr"/>
       <c r="G426" t="inlineStr">
         <is>
           <t>WO2022225934.png</t>
@@ -17375,7 +17686,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -17416,7 +17726,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -17457,7 +17766,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -17498,7 +17806,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -17539,7 +17846,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -17565,7 +17871,6 @@
       <c r="E431" t="n">
         <v>248</v>
       </c>
-      <c r="F431" t="inlineStr"/>
       <c r="G431" t="inlineStr">
         <is>
           <t>WO2023059581.png</t>
@@ -17573,10 +17878,14 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I431" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic core and substituents preserved (range-ID patent)</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -17617,7 +17926,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -17658,7 +17966,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -17684,7 +17991,6 @@
       <c r="E434" t="n">
         <v>40</v>
       </c>
-      <c r="F434" t="inlineStr"/>
       <c r="G434" t="inlineStr">
         <is>
           <t>WO2023070120.png</t>
@@ -17695,7 +18001,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -17736,7 +18041,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -17762,7 +18066,6 @@
       <c r="E436" t="n">
         <v>95</v>
       </c>
-      <c r="F436" t="inlineStr"/>
       <c r="G436" t="inlineStr">
         <is>
           <t>WO2023077046.png</t>
@@ -17773,7 +18076,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -17814,7 +18116,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -17840,7 +18141,6 @@
       <c r="E438" t="n">
         <v>55</v>
       </c>
-      <c r="F438" t="inlineStr"/>
       <c r="G438" t="inlineStr">
         <is>
           <t>WO2023078369.png</t>
@@ -17851,7 +18151,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -17892,7 +18191,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -17918,7 +18216,6 @@
       <c r="E440" t="n">
         <v>139</v>
       </c>
-      <c r="F440" t="inlineStr"/>
       <c r="G440" t="inlineStr">
         <is>
           <t>WO2023086799.png</t>
@@ -17929,7 +18226,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -17970,7 +18266,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -17996,7 +18291,6 @@
       <c r="E442" t="n">
         <v>150</v>
       </c>
-      <c r="F442" t="inlineStr"/>
       <c r="G442" t="inlineStr">
         <is>
           <t>WO2023086800.png</t>
@@ -18007,7 +18301,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -18048,7 +18341,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -18074,7 +18366,6 @@
       <c r="E444" t="n">
         <v>85</v>
       </c>
-      <c r="F444" t="inlineStr"/>
       <c r="G444" t="inlineStr">
         <is>
           <t>WO2023086801.png</t>
@@ -18085,7 +18376,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -18111,7 +18401,6 @@
       <c r="E445" t="n">
         <v>153</v>
       </c>
-      <c r="F445" t="inlineStr"/>
       <c r="G445" t="inlineStr">
         <is>
           <t>WO2023138612.png</t>
@@ -18119,10 +18408,14 @@
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I445" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -18160,10 +18453,14 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I446" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>Heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -18201,10 +18498,14 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I447" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>Heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -18245,7 +18546,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -18286,7 +18586,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -18324,10 +18623,14 @@
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I450" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -18353,7 +18656,6 @@
       <c r="E451" t="n">
         <v>199</v>
       </c>
-      <c r="F451" t="inlineStr"/>
       <c r="G451" t="inlineStr">
         <is>
           <t>WO2023193054.png</t>
@@ -18361,10 +18663,14 @@
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I451" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -18402,10 +18708,14 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I452" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -18443,10 +18753,14 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I453" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -18484,10 +18798,14 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I454" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>Heterocyclic core and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -18513,7 +18831,6 @@
       <c r="E455" t="n">
         <v>67</v>
       </c>
-      <c r="F455" t="inlineStr"/>
       <c r="G455" t="inlineStr">
         <is>
           <t>WO2023275230.png</t>
@@ -18521,10 +18838,14 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I455" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>Heterocyclic core and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -18550,7 +18871,6 @@
       <c r="E456" t="n">
         <v>70</v>
       </c>
-      <c r="F456" t="inlineStr"/>
       <c r="G456" t="inlineStr">
         <is>
           <t>WO2023283369.png</t>
@@ -18561,7 +18881,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -18602,7 +18921,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -18628,7 +18946,6 @@
       <c r="E458" t="n">
         <v>51</v>
       </c>
-      <c r="F458" t="inlineStr"/>
       <c r="G458" t="inlineStr">
         <is>
           <t>WO2024012572.png</t>
@@ -18639,7 +18956,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -18680,7 +18996,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -18721,7 +19036,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
@@ -18759,10 +19073,14 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I461" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
@@ -18788,7 +19106,6 @@
       <c r="E462" t="n">
         <v>31</v>
       </c>
-      <c r="F462" t="inlineStr"/>
       <c r="G462" t="inlineStr">
         <is>
           <t>WO2024067463.png</t>
@@ -18796,10 +19113,14 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I462" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
@@ -18837,10 +19158,14 @@
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I463" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
@@ -18866,7 +19191,6 @@
       <c r="E464" t="n">
         <v>19</v>
       </c>
-      <c r="F464" t="inlineStr"/>
       <c r="G464" t="inlineStr">
         <is>
           <t>WO2024067708.png</t>
@@ -18874,10 +19198,14 @@
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I464" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -18918,7 +19246,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -18959,7 +19286,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -18997,10 +19323,14 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I467" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -19026,7 +19356,6 @@
       <c r="E468" t="n">
         <v>24</v>
       </c>
-      <c r="F468" t="inlineStr"/>
       <c r="G468" t="inlineStr">
         <is>
           <t>WO2024067792.png</t>
@@ -19034,10 +19363,14 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I468" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -19078,7 +19411,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -19104,7 +19436,6 @@
       <c r="E470" t="n">
         <v>214</v>
       </c>
-      <c r="F470" t="inlineStr"/>
       <c r="G470" t="inlineStr">
         <is>
           <t>WO2024073133.png</t>
@@ -19115,7 +19446,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -19153,10 +19483,14 @@
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I471" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -19194,10 +19528,14 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I472" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -19238,7 +19576,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -19264,7 +19601,6 @@
       <c r="E474" t="n">
         <v>220</v>
       </c>
-      <c r="F474" t="inlineStr"/>
       <c r="G474" t="inlineStr">
         <is>
           <t>WO2024079623.png</t>
@@ -19275,7 +19611,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -19316,7 +19651,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -19342,7 +19676,6 @@
       <c r="E476" t="n">
         <v>36</v>
       </c>
-      <c r="F476" t="inlineStr"/>
       <c r="G476" t="inlineStr">
         <is>
           <t>WO2024109918.png</t>
@@ -19353,7 +19686,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -19379,7 +19711,6 @@
       <c r="E477" t="n">
         <v>31</v>
       </c>
-      <c r="F477" t="inlineStr"/>
       <c r="G477" t="inlineStr">
         <is>
           <t>WO2024180521.png</t>
@@ -19387,10 +19718,14 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I477" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>Heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -19428,10 +19763,14 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I478" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -19469,10 +19808,14 @@
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I479" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
@@ -19498,7 +19841,6 @@
       <c r="E480" t="n">
         <v>46</v>
       </c>
-      <c r="F480" t="inlineStr"/>
       <c r="G480" t="inlineStr">
         <is>
           <t>WO2024199108.png</t>
@@ -19509,7 +19851,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
@@ -19547,10 +19888,14 @@
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I481" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
@@ -19576,7 +19921,6 @@
       <c r="E482" t="n">
         <v>42</v>
       </c>
-      <c r="F482" t="inlineStr"/>
       <c r="G482" t="inlineStr">
         <is>
           <t>WO2024199109.png</t>
@@ -19584,10 +19928,14 @@
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I482" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
@@ -19613,7 +19961,6 @@
       <c r="E483" t="n">
         <v>289</v>
       </c>
-      <c r="F483" t="inlineStr"/>
       <c r="G483" t="inlineStr">
         <is>
           <t>WO2024215923.png</t>
@@ -19624,7 +19971,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -19650,7 +19996,6 @@
       <c r="E484" t="n">
         <v>138</v>
       </c>
-      <c r="F484" t="inlineStr"/>
       <c r="G484" t="inlineStr">
         <is>
           <t>WO2024220887.png</t>
@@ -19658,10 +20003,14 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I484" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
@@ -19702,7 +20051,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
@@ -19743,7 +20091,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -19784,7 +20131,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
@@ -19825,7 +20171,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -19851,7 +20196,6 @@
       <c r="E489" t="n">
         <v>27</v>
       </c>
-      <c r="F489" t="inlineStr"/>
       <c r="G489" t="inlineStr">
         <is>
           <t>WO2024235292.png</t>
@@ -19862,7 +20206,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -19900,10 +20243,14 @@
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I490" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -19941,10 +20288,14 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I491" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -19970,7 +20321,6 @@
       <c r="E492" t="n">
         <v>14</v>
       </c>
-      <c r="F492" t="inlineStr"/>
       <c r="G492" t="inlineStr">
         <is>
           <t>WO2024251301.png</t>
@@ -19981,7 +20331,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -20022,7 +20371,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -20063,7 +20411,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
@@ -20104,7 +20451,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -20130,7 +20476,6 @@
       <c r="E496" t="n">
         <v>153</v>
       </c>
-      <c r="F496" t="inlineStr"/>
       <c r="G496" t="inlineStr">
         <is>
           <t>WO2024254602.png</t>
@@ -20141,7 +20486,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -20182,7 +20526,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -20208,7 +20551,6 @@
       <c r="E498" t="n">
         <v>62</v>
       </c>
-      <c r="F498" t="inlineStr"/>
       <c r="G498" t="inlineStr">
         <is>
           <t>WO2024255765.png</t>
@@ -20219,7 +20561,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -20260,7 +20601,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -20286,7 +20626,6 @@
       <c r="E500" t="n">
         <v>79</v>
       </c>
-      <c r="F500" t="inlineStr"/>
       <c r="G500" t="inlineStr">
         <is>
           <t>WO2024255790.png</t>
@@ -20297,7 +20636,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -20323,7 +20661,6 @@
       <c r="E501" t="n">
         <v>156</v>
       </c>
-      <c r="F501" t="inlineStr"/>
       <c r="G501" t="inlineStr">
         <is>
           <t>WO2024259048.png</t>
@@ -20334,7 +20671,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
@@ -20375,7 +20711,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
@@ -20401,7 +20736,6 @@
       <c r="E503" t="n">
         <v>226</v>
       </c>
-      <c r="F503" t="inlineStr"/>
       <c r="G503" t="inlineStr">
         <is>
           <t>WO2025014877.png</t>
@@ -20412,7 +20746,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -20453,7 +20786,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -20479,7 +20811,6 @@
       <c r="E505" t="n">
         <v>40</v>
       </c>
-      <c r="F505" t="inlineStr"/>
       <c r="G505" t="inlineStr">
         <is>
           <t>WO2025021148.png</t>
@@ -20490,7 +20821,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -20516,7 +20846,6 @@
       <c r="E506" t="n">
         <v>24</v>
       </c>
-      <c r="F506" t="inlineStr"/>
       <c r="G506" t="inlineStr">
         <is>
           <t>WO2025038857.png</t>
@@ -20524,10 +20853,14 @@
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
-        </is>
-      </c>
-      <c r="I506" t="inlineStr"/>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -20568,7 +20901,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -20594,7 +20926,6 @@
       <c r="E508" t="n">
         <v>15</v>
       </c>
-      <c r="F508" t="inlineStr"/>
       <c r="G508" t="inlineStr">
         <is>
           <t>WO2025146129.png</t>
@@ -20605,7 +20936,6 @@
           <t>待判定(配额恢复后自动补跑)</t>
         </is>
       </c>
-      <c r="I508" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K508"/>
@@ -20625,7 +20955,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -20707,7 +21037,6 @@
           <t>5.4</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>AXL enzyme IC50</t>
@@ -20740,7 +21069,6 @@
           <t>1.1</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>AXL enzyme IC50</t>
@@ -20773,7 +21101,6 @@
           <t>3.3</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>AXL enzyme IC50</t>
@@ -20806,7 +21133,6 @@
           <t>4.4</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>AXL enzyme IC50</t>
@@ -21258,7 +21584,6 @@
           <t>D</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>c-Met IC50</t>
@@ -22241,7 +22566,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
@@ -22253,9 +22578,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -22263,9 +22585,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-    </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -22308,9 +22627,6 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -22318,9 +22634,6 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -22334,9 +22647,6 @@
           <t>配额恢复后将自动补跑并更新此表（届时无需重复人工已判定行）。</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">

--- a/data/verification/verification_pending.xlsx
+++ b/data/verification/verification_pending.xlsx
@@ -633,7 +633,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -668,7 +673,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -913,7 +923,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -993,7 +1008,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1053,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1183,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1223,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1483,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1528,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1663,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1703,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1833,12 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1998,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -1978,7 +2043,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2083,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2128,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2168,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2303,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2348,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -2378,7 +2473,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2513,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2638,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2683,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -2743,7 +2858,12 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2903,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2948,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -2863,7 +2993,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -2903,7 +3038,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -2938,7 +3078,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -2978,7 +3123,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3168,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3648,12 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3688,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3728,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Decoded molecule matches the depicted structure (reconfirmed on full sheet)</t>
         </is>
       </c>
     </row>
@@ -3868,7 +4038,12 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -3903,7 +4078,12 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -4113,7 +4293,12 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4333,12 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4378,12 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4418,12 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -4513,7 +4713,12 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved (range-ID patent)</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4753,12 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved (range-ID patent)</t>
         </is>
       </c>
     </row>
@@ -4588,7 +4798,12 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -4628,7 +4843,12 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4888,12 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4928,12 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -4833,7 +5063,12 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -4873,7 +5108,12 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -4998,7 +5238,12 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -5038,7 +5283,12 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5413,12 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5453,12 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5498,12 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5543,12 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -5318,7 +5588,12 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -5353,7 +5628,12 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -5393,7 +5673,12 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5713,12 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -5468,7 +5758,12 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -5503,7 +5798,12 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -5538,7 +5838,12 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5973,12 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -5703,7 +6013,12 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -5743,7 +6058,12 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -5778,7 +6098,12 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -5818,7 +6143,12 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -5853,7 +6183,12 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -6063,7 +6398,12 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved (296-page patent)</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6443,12 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved (296-page patent)</t>
         </is>
       </c>
     </row>
@@ -6143,7 +6488,12 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6533,12 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -6223,7 +6578,12 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -6263,7 +6623,12 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -6303,7 +6668,12 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -6343,7 +6713,12 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -6473,7 +6848,12 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -6508,7 +6888,12 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -6548,7 +6933,12 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved (letter-grade assay patent)</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6978,12 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved (letter-grade assay patent)</t>
         </is>
       </c>
     </row>
@@ -6628,7 +7023,12 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -6668,7 +7068,12 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -6923,7 +7328,12 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -6963,7 +7373,12 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7508,12 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7548,12 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7763,12 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Indole-type structure preserved (reconfirmed on full sheet)</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7803,12 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Indole-type structure preserved (reconfirmed on full sheet)</t>
         </is>
       </c>
     </row>
@@ -7413,7 +7848,12 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -7453,7 +7893,12 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -7493,7 +7938,12 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -7533,7 +7983,12 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -7573,7 +8028,12 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -7613,7 +8073,12 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -7653,7 +8118,12 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -7693,7 +8163,12 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -7773,7 +8248,12 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -7813,7 +8293,12 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -7853,7 +8338,12 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -7888,7 +8378,12 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -8018,7 +8513,12 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -8053,7 +8553,12 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -8093,7 +8598,12 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -8133,7 +8643,12 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -8173,7 +8688,12 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8733,12 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -8253,7 +8778,12 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -8293,7 +8823,12 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -8333,7 +8868,12 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -8373,7 +8913,12 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -8413,7 +8958,12 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -8453,7 +9003,12 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -8583,7 +9138,12 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -8618,7 +9178,12 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -8658,7 +9223,12 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -8698,7 +9268,12 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -8733,7 +9308,12 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -8768,7 +9348,12 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -8808,7 +9393,12 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -8843,7 +9433,12 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -9138,7 +9733,12 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -9178,7 +9778,12 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9823,12 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -9253,7 +9863,12 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -9293,7 +9908,12 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -9328,7 +9948,12 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -9368,7 +9993,12 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -9408,7 +10038,12 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -9448,7 +10083,12 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -9488,7 +10128,12 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -9653,7 +10298,12 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -9693,7 +10343,12 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -9733,7 +10388,12 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -9773,7 +10433,12 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -9813,7 +10478,12 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -9853,7 +10523,12 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -9893,7 +10568,12 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -9933,7 +10613,12 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -9973,7 +10658,12 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -10008,7 +10698,12 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -10223,7 +10918,12 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10958,12 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -10298,7 +11003,12 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -10333,7 +11043,12 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -10373,7 +11088,12 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -10413,7 +11133,12 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -10453,7 +11178,12 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -10488,7 +11218,12 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -10523,7 +11258,12 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -10563,7 +11303,12 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -10598,7 +11343,12 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -10638,7 +11388,12 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -10673,7 +11428,12 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -10803,7 +11563,12 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -10838,7 +11603,12 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -11048,7 +11818,12 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved (range-ID-heavy patent)</t>
         </is>
       </c>
     </row>
@@ -11168,7 +11943,12 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -11293,7 +12073,12 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -11328,7 +12113,12 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -11368,7 +12158,12 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -11408,7 +12203,12 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -11448,7 +12248,12 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>Both picks reproduce the fused polycyclic core (reconfirmed on full sheet)</t>
         </is>
       </c>
     </row>
@@ -11483,7 +12288,12 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>Both picks reproduce the fused polycyclic core (reconfirmed on full sheet)</t>
         </is>
       </c>
     </row>
@@ -11738,7 +12548,12 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -11778,7 +12593,12 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -11818,7 +12638,12 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -11853,7 +12678,12 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -11978,7 +12808,12 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -12013,7 +12848,12 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -12053,7 +12893,12 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -12093,7 +12938,12 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -12133,7 +12983,12 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -12168,7 +13023,12 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -12298,7 +13158,12 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -12333,7 +13198,12 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -12588,7 +13458,12 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved (HPK1)</t>
         </is>
       </c>
     </row>
@@ -12623,7 +13498,12 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved (HPK1)</t>
         </is>
       </c>
     </row>
@@ -12663,7 +13543,12 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -12698,7 +13583,12 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -12868,7 +13758,12 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -12908,7 +13803,12 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -12948,7 +13848,12 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -12983,7 +13888,12 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -13023,7 +13933,12 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -13058,7 +13973,12 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -13098,7 +14018,12 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -13133,7 +14058,12 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -13263,7 +14193,12 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -13298,7 +14233,12 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -13428,7 +14368,12 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved (AXL/MER/TYRO3)</t>
         </is>
       </c>
     </row>
@@ -13468,7 +14413,12 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved (AXL/MER/TYRO3)</t>
         </is>
       </c>
     </row>
@@ -13683,7 +14633,12 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -13723,7 +14678,12 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -13763,7 +14723,12 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -13803,7 +14768,12 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -13928,7 +14898,12 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -13963,7 +14938,12 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -14003,7 +14983,12 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -14038,7 +15023,12 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -14078,7 +15068,12 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -14113,7 +15108,12 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -14153,7 +15153,12 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -14188,7 +15193,12 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -14223,7 +15233,12 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -14353,7 +15368,12 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -14393,7 +15413,12 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -14433,7 +15458,12 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>Decoded structure visually corresponds to a structure on the page (reconfirmed on full sheet)</t>
         </is>
       </c>
     </row>
@@ -14468,7 +15498,12 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>Decoded structure visually corresponds to a structure on the page (reconfirmed on full sheet)</t>
         </is>
       </c>
     </row>
@@ -14508,7 +15543,12 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -14543,7 +15583,12 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -14933,7 +15978,12 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -14973,7 +16023,12 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved (NLRP3, 128p)</t>
         </is>
       </c>
     </row>
@@ -15008,7 +16063,12 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved (NLRP3, 128p)</t>
         </is>
       </c>
     </row>
@@ -15043,7 +16103,12 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -15078,7 +16143,12 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -15118,7 +16188,12 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -15153,7 +16228,12 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -15368,7 +16448,12 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -15403,7 +16488,12 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -15528,7 +16618,12 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -15563,7 +16658,12 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -15603,7 +16703,12 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -15643,7 +16748,12 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -15773,7 +16883,12 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -15813,7 +16928,12 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -15848,7 +16968,12 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -16103,7 +17228,12 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -16143,7 +17273,12 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -16183,7 +17318,12 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -16218,7 +17358,12 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -16258,7 +17403,12 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved (NLRP3)</t>
         </is>
       </c>
     </row>
@@ -16298,7 +17448,12 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved (NLRP3)</t>
         </is>
       </c>
     </row>
@@ -16518,7 +17673,12 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -16558,7 +17718,12 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -16598,7 +17763,12 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -16633,7 +17803,12 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -16673,7 +17848,12 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -16708,7 +17888,12 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -16838,7 +18023,12 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -16878,7 +18068,12 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -17008,7 +18203,12 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -17043,7 +18243,12 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -17083,7 +18288,12 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -17118,7 +18328,12 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -17243,7 +18458,12 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -17278,7 +18498,12 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -17408,7 +18633,12 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -17443,7 +18673,12 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -17478,7 +18713,12 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved (NLRP3, 204p)</t>
         </is>
       </c>
     </row>
@@ -17648,7 +18888,12 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -17683,7 +18928,12 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -17723,7 +18973,12 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -17763,7 +19018,12 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -17803,7 +19063,12 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -17843,7 +19108,12 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -17923,7 +19193,12 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -17963,7 +19238,12 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -17998,7 +19278,12 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -18038,7 +19323,12 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -18073,7 +19363,12 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -18113,7 +19408,12 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -18148,7 +19448,12 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -18188,7 +19493,12 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -18223,7 +19533,12 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -18263,7 +19578,12 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -18298,7 +19618,12 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -18338,7 +19663,12 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -18373,7 +19703,12 @@
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -18543,7 +19878,12 @@
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -18583,7 +19923,12 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -18878,7 +20223,12 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -18918,7 +20268,12 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -18953,7 +20308,12 @@
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -18993,7 +20353,12 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -19033,7 +20398,12 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -19243,7 +20613,12 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -19283,7 +20658,12 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -19408,7 +20788,12 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -19443,7 +20828,12 @@
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -19573,7 +20963,12 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -19608,7 +21003,12 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -19648,7 +21048,12 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -19683,7 +21088,12 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -19848,7 +21258,12 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -19968,7 +21383,12 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -20048,7 +21468,12 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -20088,7 +21513,12 @@
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -20128,7 +21558,12 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -20168,7 +21603,12 @@
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -20203,7 +21643,12 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -20328,7 +21773,12 @@
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -20368,7 +21818,12 @@
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -20408,7 +21863,12 @@
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -20448,7 +21908,12 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -20483,7 +21948,12 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -20523,7 +21993,12 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -20558,7 +22033,12 @@
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -20598,7 +22078,12 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -20633,7 +22118,12 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -20668,7 +22158,12 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -20708,7 +22203,12 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -20743,7 +22243,12 @@
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -20783,7 +22288,12 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -20818,7 +22328,12 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -20898,7 +22413,12 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
@@ -20933,7 +22453,12 @@
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>待判定(配额恢复后自动补跑)</t>
+          <t>match (visual)</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>Fused heterocyclic system and substituents preserved</t>
         </is>
       </c>
     </row>
